--- a/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 16,16</t>
+          <t>-6,84; 15,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 5,79</t>
+          <t>-16,82; 5,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,61; 63,75</t>
+          <t>45,8; 62,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 9,37</t>
+          <t>-12,59; 9,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 6,34</t>
+          <t>-16,88; 3,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,8; 61,54</t>
+          <t>43,82; 61,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 9,84</t>
+          <t>-5,9; 9,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 2,22</t>
+          <t>-14,23; 1,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,59; 61,21</t>
+          <t>48,51; 60,31</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 55,75</t>
+          <t>-17,16; 52,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 19,52</t>
+          <t>-43,39; 16,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111,42; 235,07</t>
+          <t>108,12; 224,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 29,15</t>
+          <t>-27,94; 29,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 19,32</t>
+          <t>-39,41; 11,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,73; 192,55</t>
+          <t>94,13; 188,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 29,52</t>
+          <t>-14,52; 29,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,89; 6,58</t>
+          <t>-35,68; 4,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>116,87; 194,53</t>
+          <t>117,74; 188,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 8,79</t>
+          <t>-10,59; 8,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 3,54</t>
+          <t>-15,69; 2,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,08; 54,1</t>
+          <t>36,16; 54,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 6,61</t>
+          <t>-11,53; 5,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 1,48</t>
+          <t>-15,32; 1,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,03; 52,94</t>
+          <t>37,77; 53,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 4,88</t>
+          <t>-8,13; 5,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -0,35</t>
+          <t>-14,26; -1,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,5; 51,46</t>
+          <t>40,21; 51,85</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 25,32</t>
+          <t>-24,17; 24,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 10,81</t>
+          <t>-36,39; 6,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,36; 165,39</t>
+          <t>81,01; 161,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 20,92</t>
+          <t>-27,18; 18,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 4,09</t>
+          <t>-36,04; 4,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,6; 164,19</t>
+          <t>87,79; 168,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 14,72</t>
+          <t>-20,14; 15,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,57; -0,83</t>
+          <t>-33,98; -3,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,73; 153,1</t>
+          <t>96,31; 155,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 8,62</t>
+          <t>-11,37; 9,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 8,85</t>
+          <t>-10,95; 8,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,31; 63,71</t>
+          <t>45,74; 63,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 11,96</t>
+          <t>-8,04; 11,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 12,41</t>
+          <t>-7,66; 12,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,2; 61,12</t>
+          <t>43,76; 60,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 7,37</t>
+          <t>-6,48; 8,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,52</t>
+          <t>-5,8; 8,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,22; 59,69</t>
+          <t>47,59; 59,56</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 30,08</t>
+          <t>-29,43; 32,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 31,21</t>
+          <t>-27,72; 29,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>110,1; 223,02</t>
+          <t>114,48; 225,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 40,13</t>
+          <t>-20,72; 40,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 42,97</t>
+          <t>-18,99; 43,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>107,81; 221,74</t>
+          <t>106,1; 217,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 23,95</t>
+          <t>-17,06; 27,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 23,79</t>
+          <t>-15,01; 26,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120,64; 198,66</t>
+          <t>120,53; 197,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 5,62</t>
+          <t>-12,9; 5,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 9,85</t>
+          <t>-7,92; 9,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,88; 54,05</t>
+          <t>37,0; 53,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 4,0</t>
+          <t>-14,08; 2,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 9,07</t>
+          <t>-7,87; 8,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,94; 59,08</t>
+          <t>43,5; 59,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 1,54</t>
+          <t>-10,63; 1,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 6,39</t>
+          <t>-5,77; 6,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,66; 54,42</t>
+          <t>42,95; 54,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 19,39</t>
+          <t>-33,49; 18,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 31,85</t>
+          <t>-20,36; 31,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92,01; 186,13</t>
+          <t>93,71; 186,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 14,98</t>
+          <t>-37,71; 8,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 31,07</t>
+          <t>-20,97; 29,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>110,61; 210,93</t>
+          <t>112,68; 215,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 5,8</t>
+          <t>-29,21; 5,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 21,45</t>
+          <t>-15,7; 21,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>112,51; 182,77</t>
+          <t>115,66; 185,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,2</t>
+          <t>-5,96; 4,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,52</t>
+          <t>-7,44; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,29; 54,56</t>
+          <t>46,21; 54,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,28</t>
+          <t>-7,0; 2,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,71</t>
+          <t>-7,09; 2,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,15; 54,12</t>
+          <t>46,52; 54,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,99</t>
+          <t>-4,86; 1,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,69</t>
+          <t>-6,07; 0,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,46; 53,16</t>
+          <t>47,18; 53,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 12,82</t>
+          <t>-15,9; 11,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 4,43</t>
+          <t>-20,07; 6,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115,97; 169,33</t>
+          <t>120,52; 167,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 6,92</t>
+          <t>-18,68; 7,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 5,34</t>
+          <t>-18,7; 6,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>118,28; 165,08</t>
+          <t>121,04; 166,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 6,01</t>
+          <t>-12,96; 5,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 2,12</t>
+          <t>-16,37; 1,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>126,38; 159,12</t>
+          <t>125,01; 159,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 15,51</t>
+          <t>-6,66; 15,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 5,13</t>
+          <t>-16,93; 4,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,8; 62,98</t>
+          <t>45,59; 63,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 9,86</t>
+          <t>-10,94; 9,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 3,97</t>
+          <t>-16,7; 4,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,82; 61,16</t>
+          <t>45,29; 62,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 9,59</t>
+          <t>-5,72; 8,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 1,44</t>
+          <t>-13,28; 1,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,51; 60,31</t>
+          <t>48,75; 60,61</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 52,83</t>
+          <t>-15,61; 53,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 16,89</t>
+          <t>-43,33; 13,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108,12; 224,38</t>
+          <t>112,67; 232,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 29,61</t>
+          <t>-25,16; 28,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 11,42</t>
+          <t>-39,12; 13,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,13; 188,33</t>
+          <t>100,96; 193,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 29,4</t>
+          <t>-13,95; 27,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 4,49</t>
+          <t>-33,19; 4,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>117,74; 188,47</t>
+          <t>118,31; 192,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 8,32</t>
+          <t>-10,95; 8,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 2,22</t>
+          <t>-16,51; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,16; 54,1</t>
+          <t>35,57; 54,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 5,96</t>
+          <t>-10,99; 6,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 1,33</t>
+          <t>-15,75; 0,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,77; 53,37</t>
+          <t>37,4; 52,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 5,18</t>
+          <t>-8,34; 4,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -1,3</t>
+          <t>-13,37; -1,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,21; 51,85</t>
+          <t>39,49; 51,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 24,13</t>
+          <t>-25,65; 24,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,39; 6,05</t>
+          <t>-36,69; 5,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,01; 161,46</t>
+          <t>79,88; 167,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 18,64</t>
+          <t>-26,35; 21,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 4,83</t>
+          <t>-37,41; 2,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,79; 168,92</t>
+          <t>86,59; 164,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 15,17</t>
+          <t>-20,64; 12,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,98; -3,75</t>
+          <t>-32,68; -3,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>96,31; 155,93</t>
+          <t>95,27; 153,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 9,09</t>
+          <t>-11,94; 7,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 8,83</t>
+          <t>-11,39; 7,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,74; 63,3</t>
+          <t>45,41; 63,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 11,77</t>
+          <t>-7,27; 11,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 12,46</t>
+          <t>-7,89; 12,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,76; 60,8</t>
+          <t>43,89; 60,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 8,13</t>
+          <t>-7,3; 7,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 8,25</t>
+          <t>-6,21; 7,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,59; 59,56</t>
+          <t>47,94; 60,19</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 32,46</t>
+          <t>-30,24; 26,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 29,77</t>
+          <t>-29,15; 25,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114,48; 225,79</t>
+          <t>111,18; 225,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 40,96</t>
+          <t>-18,75; 39,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 43,24</t>
+          <t>-19,53; 43,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>106,1; 217,61</t>
+          <t>105,78; 215,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 27,14</t>
+          <t>-18,72; 24,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 26,73</t>
+          <t>-16,06; 25,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120,53; 197,68</t>
+          <t>120,92; 199,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 5,47</t>
+          <t>-12,53; 4,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 9,66</t>
+          <t>-7,84; 9,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,0; 53,85</t>
+          <t>36,74; 53,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 2,32</t>
+          <t>-13,64; 3,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 8,7</t>
+          <t>-8,76; 9,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,5; 59,5</t>
+          <t>43,31; 58,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 1,52</t>
+          <t>-10,73; 1,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,58</t>
+          <t>-5,48; 6,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,95; 54,57</t>
+          <t>43,24; 54,37</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 18,0</t>
+          <t>-32,74; 17,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 31,42</t>
+          <t>-20,86; 33,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93,71; 186,31</t>
+          <t>94,12; 188,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 8,56</t>
+          <t>-37,78; 13,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 29,6</t>
+          <t>-23,49; 30,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>112,68; 215,9</t>
+          <t>110,02; 210,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 5,0</t>
+          <t>-29,35; 5,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 21,91</t>
+          <t>-14,98; 21,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>115,66; 185,41</t>
+          <t>116,29; 186,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 4,02</t>
+          <t>-6,15; 3,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 2,15</t>
+          <t>-7,17; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46,21; 54,72</t>
+          <t>45,7; 55,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 2,52</t>
+          <t>-6,69; 2,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,08</t>
+          <t>-6,88; 2,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,52; 54,27</t>
+          <t>46,23; 54,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,97</t>
+          <t>-4,78; 2,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 0,52</t>
+          <t>-6,36; 0,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,18; 53,37</t>
+          <t>47,43; 53,5</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 11,94</t>
+          <t>-16,22; 11,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 6,49</t>
+          <t>-19,14; 6,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>120,52; 167,99</t>
+          <t>118,79; 173,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 7,94</t>
+          <t>-17,66; 8,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 6,28</t>
+          <t>-18,53; 7,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>121,04; 166,46</t>
+          <t>119,8; 167,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 5,72</t>
+          <t>-12,91; 6,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 1,51</t>
+          <t>-17,18; 1,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>125,01; 159,86</t>
+          <t>126,73; 161,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53,55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-5,87</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,12</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,78</t>
+          <t>55,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54,52</t>
+          <t>54,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 15,13</t>
+          <t>-11,45; 9,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 4,05</t>
+          <t>-17,41; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,59; 63,95</t>
+          <t>44,78; 61,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 9,58</t>
+          <t>-6,14; 16,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 4,64</t>
+          <t>-16,54; 5,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,29; 62,03</t>
+          <t>45,99; 63,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 8,85</t>
+          <t>-6,18; 9,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 1,59</t>
+          <t>-13,36; 2,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,75; 60,61</t>
+          <t>48,51; 61,24</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-2,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-15,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>138,75%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>12,3%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-17,21%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>161,99%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,85%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>139,33%</t>
+          <t>163,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149,43%</t>
+          <t>149,33%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 53,6</t>
+          <t>-26,3; 29,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 13,4</t>
+          <t>-39,51; 19,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112,67; 232,6</t>
+          <t>96,62; 191,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,16; 28,9</t>
+          <t>-16,01; 55,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 13,77</t>
+          <t>-43,17; 19,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>100,96; 193,05</t>
+          <t>112,14; 234,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 27,1</t>
+          <t>-16,17; 29,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 4,8</t>
+          <t>-33,89; 6,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>118,31; 192,13</t>
+          <t>116,68; 193,14</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-6,97</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45,74</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-6,83</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46,43</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,31</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,97</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,96</t>
+          <t>48,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>46,1</t>
+          <t>46,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 8,18</t>
+          <t>-10,78; 6,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 1,89</t>
+          <t>-16,33; 1,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,57; 54,83</t>
+          <t>38,01; 52,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 6,56</t>
+          <t>-11,1; 8,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 0,67</t>
+          <t>-15,31; 3,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,4; 52,84</t>
+          <t>39,9; 55,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 4,37</t>
+          <t>-8,02; 4,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,37; -1,02</t>
+          <t>-12,62; -0,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,49; 51,5</t>
+          <t>40,91; 51,98</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-6,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-18,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>123,01%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-3,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-17,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>120,5%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-6,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-18,74%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>123,6%</t>
+          <t>126,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>121,91%</t>
+          <t>124,16%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 24,0</t>
+          <t>-26,57; 20,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 5,72</t>
+          <t>-39,07; 4,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,88; 167,36</t>
+          <t>87,06; 163,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 21,02</t>
+          <t>-26,22; 25,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 2,14</t>
+          <t>-36,25; 10,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,59; 164,28</t>
+          <t>88,08; 171,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 12,62</t>
+          <t>-19,52; 14,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -3,02</t>
+          <t>-30,57; -0,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,27; 153,94</t>
+          <t>95,84; 155,12</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52,55</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,06</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>54,82</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52,74</t>
+          <t>54,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53,8</t>
+          <t>53,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 7,97</t>
+          <t>-7,79; 11,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 7,52</t>
+          <t>-7,43; 12,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,41; 63,35</t>
+          <t>44,0; 60,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 11,51</t>
+          <t>-11,52; 8,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 12,37</t>
+          <t>-10,67; 8,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,89; 60,41</t>
+          <t>45,73; 61,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 7,6</t>
+          <t>-6,74; 7,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 7,97</t>
+          <t>-6,56; 7,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,94; 60,19</t>
+          <t>47,04; 59,17</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>153,61%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-5,52%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-3,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158,33%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>154,18%</t>
+          <t>156,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>156,35%</t>
+          <t>155,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 26,94</t>
+          <t>-19,56; 40,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 25,32</t>
+          <t>-19,26; 42,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>111,18; 225,12</t>
+          <t>107,79; 222,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 39,67</t>
+          <t>-30,09; 30,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 43,14</t>
+          <t>-26,64; 31,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>105,78; 215,19</t>
+          <t>109,29; 218,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 24,8</t>
+          <t>-17,85; 23,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 25,93</t>
+          <t>-17,44; 23,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120,92; 199,69</t>
+          <t>118,62; 197,69</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-5,12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51,23</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-3,91</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,66</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45,88</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,58</t>
+          <t>47,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48,81</t>
+          <t>49,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 4,93</t>
+          <t>-13,79; 4,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 9,5</t>
+          <t>-8,61; 9,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,74; 53,36</t>
+          <t>42,57; 58,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 3,57</t>
+          <t>-12,68; 5,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 9,13</t>
+          <t>-7,99; 9,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,31; 58,54</t>
+          <t>38,4; 55,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 1,79</t>
+          <t>-11,15; 1,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 6,56</t>
+          <t>-5,57; 6,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43,24; 54,37</t>
+          <t>43,49; 54,65</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-15,4%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>154,08%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-11,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>133,85%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-15,4%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>155,14%</t>
+          <t>137,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>144,5%</t>
+          <t>145,59%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 17,64</t>
+          <t>-35,76; 14,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 33,07</t>
+          <t>-23,83; 31,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,12; 188,18</t>
+          <t>109,75; 209,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 13,89</t>
+          <t>-33,64; 19,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 30,93</t>
+          <t>-20,71; 31,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>110,02; 210,97</t>
+          <t>94,52; 189,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 5,08</t>
+          <t>-29,84; 5,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 21,71</t>
+          <t>-15,43; 21,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>116,29; 186,62</t>
+          <t>115,04; 183,75</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,61</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>50,18</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,83</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>50,43</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,47</t>
+          <t>51,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50,46</t>
+          <t>50,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,87</t>
+          <t>-7,64; 2,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,15</t>
+          <t>-7,6; 1,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,7; 55,15</t>
+          <t>45,66; 53,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,73</t>
+          <t>-5,59; 4,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,56</t>
+          <t>-7,89; 1,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,23; 54,45</t>
+          <t>46,14; 55,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,22</t>
+          <t>-5,01; 1,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,38</t>
+          <t>-5,93; 0,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,43; 53,5</t>
+          <t>47,75; 53,13</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-5,44%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-7,32%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>140,57%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-2,83%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-7,99%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>142,58%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-5,44%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-7,32%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>141,39%</t>
+          <t>144,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>141,99%</t>
+          <t>142,54%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 11,55</t>
+          <t>-20,19; 6,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 6,48</t>
+          <t>-19,78; 5,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118,79; 173,53</t>
+          <t>117,16; 164,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 8,13</t>
+          <t>-14,93; 12,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 7,6</t>
+          <t>-21,13; 4,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>119,8; 167,91</t>
+          <t>118,38; 170,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 6,75</t>
+          <t>-13,32; 6,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 1,16</t>
+          <t>-16,0; 2,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>126,73; 161,12</t>
+          <t>127,14; 159,94</t>
         </is>
       </c>
     </row>
